--- a/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
+++ b/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -160,6 +160,12 @@
     <t>1</t>
   </si>
   <si>
+    <t>NPU02193</t>
+  </si>
+  <si>
+    <t>P(kB;fPt)—Glucose; stofk. = ? mmol/L</t>
+  </si>
+  <si>
     <t>NPU03011</t>
   </si>
   <si>
@@ -212,6 +218,30 @@
   </si>
   <si>
     <t>P—C-reaktivt protein; massek. = ? mg/L</t>
+  </si>
+  <si>
+    <t>DNK05463</t>
+  </si>
+  <si>
+    <t>Ankel(højre)—Blodtryk(systolisk); tryk(liggende) = ? mmHg</t>
+  </si>
+  <si>
+    <t>DNK05465</t>
+  </si>
+  <si>
+    <t>Tå(højre)—Blodtryk(systolisk); tryk(liggende) = ? mmHg</t>
+  </si>
+  <si>
+    <t>DNK05467</t>
+  </si>
+  <si>
+    <t>Ankel(venstre)—Blodtryk(systolisk); tryk(liggende) = ? mmHg</t>
+  </si>
+  <si>
+    <t>DNK05469</t>
+  </si>
+  <si>
+    <t>Tå(venstre)—Blodtryk(systolisk); tryk(liggende) = ? mmHg</t>
   </si>
   <si>
     <t>DNK05472</t>
@@ -581,7 +611,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -735,7 +765,7 @@
         <v>67</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -743,13 +773,83 @@
         <v>47</v>
       </c>
       <c r="B12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="D12" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D12" t="s" s="2">
+      <c r="C13" t="s" s="2">
         <v>71</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
+++ b/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
+++ b/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
+++ b/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
+++ b/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
+++ b/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
+++ b/fhir/CodeSystem-1.2.208.176.2.1--20190829.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
